--- a/data/FAMD_dimensions.xlsx
+++ b/data/FAMD_dimensions.xlsx
@@ -11,92 +11,6 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>Dimension</t>
-  </si>
-  <si>
-    <t>Eigenvalue</t>
-  </si>
-  <si>
-    <t>Explained Variance (%)</t>
-  </si>
-  <si>
-    <t>Cumulative Variance (%)</t>
-  </si>
-  <si>
-    <t>Top Contributing Variables</t>
-  </si>
-  <si>
-    <t>Dim.1</t>
-  </si>
-  <si>
-    <t>tuitionnn, inst_type, awardlev</t>
-  </si>
-  <si>
-    <t>Dim.2</t>
-  </si>
-  <si>
-    <t>num_degrees, i_total_pop, awardlev</t>
-  </si>
-  <si>
-    <t>Dim.3</t>
-  </si>
-  <si>
-    <t>pell, nonwhite, msi</t>
-  </si>
-  <si>
-    <t>Dim.4</t>
-  </si>
-  <si>
-    <t>special_focus, msi, nonwhite</t>
-  </si>
-  <si>
-    <t>Dim.5</t>
-  </si>
-  <si>
-    <t>special_focus, inst_type, awardlev</t>
-  </si>
-  <si>
-    <t>Dim.6</t>
-  </si>
-  <si>
-    <t>inst_type, special_focus, msi</t>
-  </si>
-  <si>
-    <t>Dim.7</t>
-  </si>
-  <si>
-    <t>special_focus, msi, evening</t>
-  </si>
-  <si>
-    <t>Dim.8</t>
-  </si>
-  <si>
-    <t>special_focus, msi, awardlev</t>
-  </si>
-  <si>
-    <t>Dim.9</t>
-  </si>
-  <si>
-    <t>msi, special_focus, system</t>
-  </si>
-  <si>
-    <t>Dim.10</t>
-  </si>
-  <si>
-    <t>special_focus, awardlev, online_progs</t>
-  </si>
-  <si>
-    <t>Dim.11</t>
-  </si>
-  <si>
-    <t>Dim.12</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,26 +354,38 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Eigenvalue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Explained Variance (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Variance (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Top Contributing Variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dim.1</t>
+        </is>
       </c>
       <c r="B2">
         <v>4.52</v>
@@ -470,13 +396,17 @@
       <c r="D2">
         <v>16.76</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>7</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tuitionnn, inst_type, awardlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dim.2</t>
+        </is>
       </c>
       <c r="B3">
         <v>2.93</v>
@@ -487,13 +417,17 @@
       <c r="D3">
         <v>27.62</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>9</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>num_degrees, i_total_pop, awardlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dim.3</t>
+        </is>
       </c>
       <c r="B4">
         <v>2.08</v>
@@ -504,13 +438,17 @@
       <c r="D4">
         <v>35.32</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>11</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pell, nonwhite, msi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dim.4</t>
+        </is>
       </c>
       <c r="B5">
         <v>1.9</v>
@@ -521,13 +459,17 @@
       <c r="D5">
         <v>42.36</v>
       </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>13</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>special_focus, msi, nonwhite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dim.5</t>
+        </is>
       </c>
       <c r="B6">
         <v>1.57</v>
@@ -538,13 +480,17 @@
       <c r="D6">
         <v>48.16</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>15</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>special_focus, inst_type, awardlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dim.6</t>
+        </is>
       </c>
       <c r="B7">
         <v>1.33</v>
@@ -555,13 +501,17 @@
       <c r="D7">
         <v>53.1</v>
       </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>17</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>inst_type, special_focus, msi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dim.7</t>
+        </is>
       </c>
       <c r="B8">
         <v>1.13</v>
@@ -572,13 +522,17 @@
       <c r="D8">
         <v>57.28</v>
       </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>19</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>special_focus, msi, evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dim.8</t>
+        </is>
       </c>
       <c r="B9">
         <v>1.1</v>
@@ -589,13 +543,17 @@
       <c r="D9">
         <v>61.35</v>
       </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>21</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>special_focus, msi, awardlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dim.9</t>
+        </is>
       </c>
       <c r="B10">
         <v>1.05</v>
@@ -606,13 +564,17 @@
       <c r="D10">
         <v>65.23</v>
       </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>23</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>msi, special_focus, system</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dim.10</t>
+        </is>
       </c>
       <c r="B11">
         <v>1.01</v>
@@ -623,13 +585,17 @@
       <c r="D11">
         <v>68.97</v>
       </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>25</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>special_focus, awardlev, online_progs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dim.11</t>
+        </is>
       </c>
       <c r="B12">
         <v>0.99</v>
@@ -640,13 +606,17 @@
       <c r="D12">
         <v>72.64</v>
       </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>26</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>special_focus, msi, awardlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dim.12</t>
+        </is>
       </c>
       <c r="B13">
         <v>0.88</v>
@@ -657,8 +627,10 @@
       <c r="D13">
         <v>75.88</v>
       </c>
-      <c r="E13" t="s">
-        <v>20</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>special_focus, msi, awardlev</t>
+        </is>
       </c>
     </row>
   </sheetData>
